--- a/Final_Project_Cases.xlsx
+++ b/Final_Project_Cases.xlsx
@@ -34,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,11 +44,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -92,9 +87,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -462,17 +454,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -483,35 +476,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>Student Name (First Last)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>LLM Model Name Used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Original Code Snippet</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>New Code Snippet with Bugs</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Your Initial Self-Reflection</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>GenAI's Label (Good/Bad)</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>GenAI's Label ("Good" or "Bad")</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>GenAI's Guidance</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Your New Self-Reflection</t>
         </is>
@@ -528,30 +526,39 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>X_test_scaled = scaler.transform(X_test)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>X_test_scaled = scaler.fit_transform(X_test)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>I changed scaler.transform(X_test) to scaler.fit_transform(X_test). The test accuracy is slightly lower than expected. I think this is because calling fit_transform on the test set recalculates the mean and standard deviation from the test data alone, which differs from the training data statistics. The model was trained on features normalized with training statistics, but during evaluation it sees features normalized with different statistics, so the distributions no longer match and the model's learned weights are misapplied.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Your reflection correctly identifies the core issue: fitting the scaler on the test set introduces a mismatch between how training and test features are normalized. This is a classic data leakage / distribution mismatch problem. Good reasoning.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>i changed transform to fit_transform on the test set and my accuracy went down a little bit. i think its because the scaling is off somehow since i changed how the test data is being processed</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Your reflection notices the accuracy dropped but doesn't explain the mechanism. Think more carefully about what 'fit' actually does versus 'transform' alone. When you call fit on the test set, what statistics does it compute? Where were those statistics supposed to come from? What happens to the model's expectations about the input distribution when training and test data are normalized using different statistics?</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ok so fit_transform on the test set recalculates the mean and std from the test data itself instead of using the training set numbers. the model was trained on features normalized with training stats, so the weights it learned only line up correctly with those specific scaled values. when i refit on the test set the values shift, like if training loudness was centered at -10dB but the test data centers at -12dB, every test sample looks slightly different to the model than it should. so the weights dont apply correctly to the shifted values, which is why accuracy drops. fix is always fit only on training data and then transform the test set with those same training stats.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -564,32 +571,37 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>criterion = nn.CrossEntropyLoss()</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>criterion = nn.MSELoss()</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>I changed the loss function from CrossEntropyLoss to MSELoss and got an error about tensor sizes not matching. I'm not sure why — MSELoss should be able to compute a loss between the model's output and the target labels.</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>I changed the loss function from CrossEntropyLoss to MSELoss and got an error about tensor sizes not matching. I'm not sure why, MSELoss should be able to compute a loss between the model's output and the target labels.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Your reflection identifies the symptom but not the cause. Think more carefully about what shapes MSELoss expects for its two inputs versus what CrossEntropyLoss expects. What is the shape of your model's output? What is the shape and dtype of your target tensor? How do those two loss functions differ in what they require from their inputs?</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>After thinking about it: MSELoss expects both inputs to have the same shape and to be floating point. My model outputs (batch_size, 10) — one logit per class — but my targets are (batch_size,) integers representing class indices. MSELoss tries to compute element-wise (output - target)^2, which fails because the shapes don't match. CrossEntropyLoss is specifically designed to accept (N, C) logits and (N,) Long integer class indices, which is the correct format for multi-class classification.</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>ok so MSELoss expects both inputs to have the same shape and both to be floats. my model outputs (batch_size, 10), basically one logit per class, but my targets are (batch_size,) ints that are class indices. MSELoss is trying to do elementwise (output - target)^2 and that just fails because the shapes dont match at all. CrossEntropyLoss is the one built to take (N, C) logits and (N,) Long ints as labels, which is what you actually want for multi-class classification.</t>
         </is>
       </c>
     </row>
@@ -603,6 +615,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>optimizer.zero_grad()
 loss = criterion(model(X_batch), y_batch)
@@ -610,7 +627,7 @@
 optimizer.step()</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t># optimizer.zero_grad()  &lt;-- removed
 loss = criterion(model(X_batch), y_batch)
@@ -618,22 +635,26 @@
 optimizer.step()</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>I removed optimizer.zero_grad() and the loss became higher and more unstable across epochs. Without clearing gradients before each backward pass, the gradients from the current batch are added on top of the gradients from all previous batches. This means each weight update uses a gradient that is the cumulative sum of many batches, making the effective update size grow over time and causing the optimization to overshoot and diverge.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Correct. Accumulated gradients produce increasingly large effective updates that push weights far past any local minimum, causing the unstable loss behavior you observed.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>i commented out optimizer.zero_grad() and the loss got higher and more unstable. i think its because the gradients arent being cleared so theyre carrying over from the last batch somehow</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>You've identified that gradients 'carry over' but haven't explained what that actually means for the weight update. Think about what PyTorch does with .backward() each time it's called: does it replace the existing gradient or add to it? If gradients accumulate across batches, what does the effective gradient look like by the 10th batch? What size of update does that produce compared to what the optimizer expects?</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>pytorch accumulates gradients by default, so .backward() adds to whatever gradient is already stored instead of replacing it. without zero_grad() the gradient by the 10th batch is the sum of 10 batches worth of gradients. the optimizer then takes a step proportional to that huge accumulated value, way bigger than intended for one batch. the weights overshoot the loss minimum and the loss spikes and diverges. its kind of like having a learning rate that grows every batch. zero_grad() just resets the stored gradient so each batch only uses its own.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -646,32 +667,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>train_loader = DataLoader(train_dataset, batch_size=256, shuffle=True)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>train_loader = DataLoader(train_dataset, batch_size=1, shuffle=True)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Setting batch_size=1 caused a ValueError. I think the error might be related to the batch size being too small for some operation in the model, but I'm not sure which layer is causing it.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>You identified that batch size is involved but not which layer fails or why. Look at the full error message: 'Expected more than 1 value per channel when training.' Which layer in your model computes statistics across the batch dimension? What does that layer need from a batch, and what happens when the batch has only one sample?</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>The error comes from BatchNorm1d. Batch normalization normalizes each feature by computing the mean and variance across all samples in the current batch. With a batch size of 1 there is only one value per channel, so variance is undefined (you cannot compute variance from a single data point). PyTorch raises a ValueError rather than silently dividing by zero. The fix is to use a batch size of at least 2, or to replace BatchNorm1d with LayerNorm or InstanceNorm which do not require multiple samples.</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>the error is coming from BatchNorm1d. batch norm needs to compute mean and variance across the samples in a batch to normalize each feature. with batch_size=1 theres only one value per channel, so variance is undefined (you cant compute variance from a single point). pytorch throws a ValueError instead of silently dividing by zero. the fix is using batch_size of at least 2, or swapping BatchNorm1d for LayerNorm or InstanceNorm which dont need multiple samples.</t>
         </is>
       </c>
     </row>
@@ -686,30 +712,39 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>y_train_tensor = torch.LongTensor(y_train)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>y_train_tensor = torch.FloatTensor(y_train)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>The error says 'expected scalar type Long but found Float'. I changed LongTensor to FloatTensor for the label tensor. CrossEntropyLoss requires target labels to be integer indices stored as Long (int64), because it uses them to index into the output logits — label 3 means 'pick the logit at position 3.' Float values cannot be used as indices, so PyTorch raises a type error.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Exactly right. CrossEntropyLoss internally uses the target as an index into the class dimension of the output, which requires integer (Long) type. Float tensors cannot serve as indices.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>i used FloatTensor instead of LongTensor for y_train and got a runtime error saying expected Long but found Float. seems like CrossEntropyLoss just needs a specific tensor type for the labels i guess</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>You've noticed the type requirement but haven't explained why it exists. Think about what CrossEntropyLoss actually does with the target values internally. It doesn't treat them as continuous numbers to do math on. What specific operation does it perform with each target value? What would happen if you tried to use 3.7 as a target? What does CrossEntropyLoss need to do with that value and why does float break it?</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>CrossEntropyLoss uses the target values as indices into the output logit vector, so label 3 means it pulls out position 3 in the output. indexing needs integers, you cant index position 3.7 or any float. pytorch throws a type error because float tensors cant serve as array indices. LongTensor (int64) works because those are valid integer indices. this is different from MSELoss, which treats targets as numeric values and would actually accept floats. CrossEntropyLoss is doing lookup, not arithmetic with the labels.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -722,32 +757,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>optimizer = torch.optim.Adam(model.parameters(), lr=0.001, weight_decay=1e-4)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>optimizer = torch.optim.Adam(model.parameters(), lr=10.0, weight_decay=1e-4)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>I changed the learning rate to 10.0 and the loss became very high and unstable. A high learning rate probably means the update steps are too large.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>You've identified the symptom correctly, but 'too large' needs more depth. Think about what happens geometrically when the step size is much larger than the curvature of the loss surface. What does overshooting a minimum mean for the next gradient? Why might the loss not just stay high, but oscillate or eventually produce NaN values?</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>With lr=10.0, each weight update is: w = w - 10.0 * gradient. The gradients in the first pass are already non-trivial, so the weights overshoot the loss minimum dramatically. After overshooting, the model is in a high-loss region with large gradients pointing in the opposite direction, causing another large overshoot. This oscillation produces a positive feedback loop where each step lands the weights in an increasingly extreme region. Eventually, weight values or intermediate activations exceed the floating point range and produce Inf or NaN, which propagates through all subsequent computations. The fix is to use a much smaller learning rate, typically in the range 1e-4 to 1e-2 for Adam.</t>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>with lr=10.0 each weight update is basically w = w - 10.0 * gradient. the gradients in the first pass are already not tiny, so the weights overshoot the loss minimum by a lot. once youre overshot, the model is in a high-loss region with big gradients pointing the other direction, so the next step overshoots again the other way. it ends up oscillating worse and worse until the weights or activations go past the float range and you get Inf or NaN, which then poisons everything downstream. fix is using a much smaller lr, like 1e-4 to 1e-2 for Adam.</t>
         </is>
       </c>
     </row>
@@ -762,34 +802,43 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>nn.Linear(input_size, 256), nn.BatchNorm1d(256), nn.ReLU(), nn.Dropout(0.3),
 nn.Linear(256, 128), nn.BatchNorm1d(128), nn.ReLU(), nn.Dropout(0.3),
 nn.Linear(128, 64), nn.BatchNorm1d(64), nn.ReLU(), nn.Dropout(0.2),</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>nn.Linear(input_size, 256), nn.BatchNorm1d(256), nn.Dropout(0.3),  # ReLU removed
 nn.Linear(256, 128), nn.BatchNorm1d(128), nn.Dropout(0.3),          # ReLU removed
 nn.Linear(128, 64), nn.BatchNorm1d(64), nn.Dropout(0.2),            # ReLU removed</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Removing all ReLU activations dropped test accuracy from ~0.43 to ~0.38. Without ReLU, each layer performs only a linear transformation (Linear + BatchNorm is still linear in terms of the function it learns). Composing multiple linear transformations is mathematically equivalent to a single linear transformation, so the depth of the network provides no additional expressiveness. The model cannot learn non-linear decision boundaries needed to separate 10 overlapping genre clusters in the audio feature space.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Well reasoned. You correctly identified the universal approximation argument: without non-linearities, a deep network collapses to a single linear map, losing all representational advantage of depth.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>i took out all the relu layers and accuracy dropped from like 0.43 to 0.38. i think the model just performs worse without them because relu helps the model learn better</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Saying ReLU 'helps the model learn better' is too vague to show real understanding. Think about what a neural network layer does mathematically. It's a linear transformation. What happens when you compose multiple linear transformations without any non-linearity between them? Is a stack of 3 linear layers mathematically equivalent to one linear layer or something more expressive? What does that imply about the kinds of patterns the network can and cannot learn?</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>without relu each layer is just a matrix multiply, so the full network becomes W3*(W2*(W1*x + b1) + b2) + b3 which simplifies down to one matrix multiply (W3*W2*W1)*x + some bias. composing linear transformations always gives you another linear transformation, no matter how many layers you stack. so a 3 layer network without activations has the same expressive power as logistic regression. it can only draw linear decision boundaries. the 10 genre clusters in audio feature space overlap in non-linear ways, so a purely linear model cant separate them well, which lines up with accuracy dropping to near-logistic-regression levels.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -802,30 +851,39 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>model = GenreClassifier(input_size=13, num_classes=10)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>model = GenreClassifier(input_size=12, num_classes=10)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>I set input_size=12 in the model but the dataset has 13 audio features. This causes a RuntimeError during the first forward pass because the weight matrix of the first Linear layer has shape (256, 12), expecting a 12-dimensional input, but the actual input tensor has shape (batch_size, 13). Matrix multiplication requires the inner dimensions to match, and 13 ≠ 12.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Correct. The Linear layer's weight matrix shape is fixed at construction time based on input_size. Any mismatch with the actual data dimension fails at the first matrix multiply in the forward pass.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>i set input_size to 12 but the data has 13 features and got a runtime error. the model just doesnt match the input data i think</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>You've identified the mismatch but not explained the mechanism that causes the crash. Think about what the first Linear layer does when it's constructed with input_size=12. What shape is the weight matrix it creates? When your actual input tensor arrives with 13 features, what operation does PyTorch attempt? What specifically about matrix multiplication requires the inner dimensions to match?</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>the first Linear layer creates a weight matrix of shape (256, 12), so 256 output neurons each expecting 12 inputs. but the actual input tensor has shape (batch_size, 13). the forward pass tries to compute (batch, 13) @ (12, 256), which is a matrix multiply where the inner dimensions are 13 and 12. matrix mult needs the columns of the left matrix to equal the rows of the right, and 13 != 12, so pytorch throws a RuntimeError right away on the first forward pass. fix is making input_size match the number of features in the dataset exactly.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -838,30 +896,39 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>model = GenreClassifier(input_size=13, num_classes=10)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>model = GenreClassifier(input_size=13, num_classes=9)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>I set num_classes=9 but there are 10 classes with labels 0 through 9. CrossEntropyLoss uses each target label as an index into the output logit vector. With 9 output neurons, valid indices are 0 through 8. When a sample with label 9 is encountered, PyTorch attempts to access index 9 in a 9-element vector, which is out of bounds, causing the IndexError.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Exactly right. CrossEntropyLoss requires that every target value satisfies 0 &lt;= target &lt; num_classes. A single out-of-range label immediately raises an IndexError.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>i changed num_classes to 9 instead of 10 and got an index error. i guess having the wrong number of classes causes problems with the labels</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>You've noted there's an index error but haven't explained why the wrong class count causes one. Think about how CrossEntropyLoss uses the num_classes value. It defines the size of the output layer. What does that mean for which target values are valid? Your dataset has labels 0 through 9. What happens when CrossEntropyLoss encounters label 9 but the output vector only has indices 0 through 8?</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>num_classes=9 means the final Linear layer outputs 9 values, so valid indices are 0 through 8. CrossEntropyLoss takes each target label as an index to look up the corresponding logit, so label 0 grabs logit[0] and label 9 would try to grab logit[9]. but logit[9] doesnt exist in a 9-element vector, thats out of bounds. the moment a sample with label 9 hits a batch pytorch throws an IndexError. since the dataset has all 10 genres (0-9), label 9 shows up almost immediately. num_classes has to match the number of unique labels in the dataset exactly.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -873,6 +940,11 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>for epoch in range(EPOCHS):
     model.train()
@@ -880,7 +952,7 @@
         ...</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>for epoch in range(EPOCHS):
     model.eval()  # BUG: should be model.train()
@@ -888,24 +960,24 @@
         ...</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>I used model.eval() instead of model.train() during the training loop. The model trained without crashing and accuracy looks similar. I'm not sure what actually changed.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>You noticed there was no crash but haven't identified what model.eval() actually changes inside the model. Which specific layer types behave differently depending on whether the model is in train or eval mode? Think about Dropout and BatchNorm — what does each one do differently in eval mode, and how does that affect what the model is learning?</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>In eval mode, two layers behave differently during what should be training: (1) Dropout is disabled — all neurons remain active, so the regularization designed to prevent overfitting is not applied. The model sees every feature on every pass, which can lead to overfitting. (2) BatchNorm1d uses its accumulated running mean and variance instead of computing fresh statistics from the current batch. Early in training these running stats are poor estimates, so normalization is less effective. Together, the model trains with weaker regularization and unstable normalization, which explains why training loss appeared lower (less dropout noise) but the model may not generalize as well as it would with proper train mode.</t>
+          <t>You noticed there was no crash but haven't identified what model.eval() actually changes inside the model. Which specific layer types behave differently depending on whether the model is in train or eval mode? Think about Dropout and BatchNorm: what does each one do differently in eval mode, and how does that affect what the model is learning?</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>in eval mode two layers act differently during what should be training. first, Dropout is disabled, so all neurons stay active and the regularization thats supposed to prevent overfitting just isnt happening. the model sees every feature on every pass which makes it easier to overfit. second, BatchNorm1d uses its accumulated running mean and variance instead of computing fresh stats from the current batch. early in training those running stats are still poor estimates so normalization works worse. between the two, the model is training with weaker regularization and less stable normalization, which explains why training loss looked lower (less dropout noise) but the model probably wont generalize as well as it would in proper train mode.</t>
         </is>
       </c>
     </row>
